--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF8F4DB-9ACB-4D2A-8169-2D96C5079E01}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0103" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0103" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -81,22 +90,34 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +125,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +356,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1058"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,93 +415,93 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
       <c r="B6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
       <c r="I8" s="1"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
       <c r="I9" s="1"/>
     </row>
-    <row r="10" ht="13.5" customHeight="1">
+    <row r="10" spans="1:12" ht="13.5" customHeight="1">
       <c r="I10" s="1"/>
     </row>
-    <row r="11" ht="13.5" customHeight="1">
+    <row r="11" spans="1:12" ht="13.5" customHeight="1">
       <c r="I11" s="1"/>
     </row>
-    <row r="12" ht="13.5" customHeight="1">
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" ht="13.5" customHeight="1">
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -489,576 +509,576 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1">
+    <row r="14" spans="1:12" ht="13.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
+    <row r="16" spans="1:12" ht="13.5" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" ht="13.5" customHeight="1">
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
       <c r="A24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="A28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
       <c r="I29" s="1"/>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
       <c r="I30" s="1"/>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
       <c r="I31" s="1"/>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
       <c r="I32" s="1"/>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
       <c r="I33" s="1"/>
     </row>
-    <row r="34" ht="13.5" customHeight="1">
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
       <c r="I34" s="1"/>
     </row>
-    <row r="35" ht="13.5" customHeight="1">
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
       <c r="I35" s="1"/>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
       <c r="I36" s="1"/>
     </row>
-    <row r="37" ht="13.5" customHeight="1">
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" ht="13.5" customHeight="1">
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
       <c r="I39" s="1"/>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
+    <row r="40" spans="1:10" ht="13.5" customHeight="1">
       <c r="I40" s="1"/>
     </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="41" spans="1:10" ht="13.5" customHeight="1">
       <c r="I41" s="1"/>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
+    <row r="42" spans="1:10" ht="13.5" customHeight="1">
       <c r="I42" s="1"/>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="43" spans="1:10" ht="13.5" customHeight="1">
       <c r="I43" s="1"/>
     </row>
-    <row r="44" ht="13.5" customHeight="1">
+    <row r="44" spans="1:10" ht="13.5" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" ht="13.5" customHeight="1">
+    <row r="45" spans="1:10" ht="13.5" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" ht="13.5" customHeight="1">
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
       <c r="A46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" ht="13.5" customHeight="1">
+    <row r="48" spans="1:10" ht="13.5" customHeight="1">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" ht="13.5" customHeight="1">
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
       <c r="A51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" ht="13.5" customHeight="1">
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="I53" s="1"/>
     </row>
-    <row r="54" ht="13.5" customHeight="1">
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="A55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" ht="13.5" customHeight="1">
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
       <c r="I56" s="1"/>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
       <c r="I57" s="1"/>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" ht="13.5" customHeight="1">
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" ht="13.5" customHeight="1">
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" ht="13.5" customHeight="1">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" ht="13.5" customHeight="1">
+    <row r="65" spans="1:10" ht="13.5" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" ht="13.5" customHeight="1">
+    <row r="66" spans="1:10" ht="13.5" customHeight="1">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
+    <row r="67" spans="1:10" ht="13.5" customHeight="1">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" ht="13.5" customHeight="1">
+    <row r="68" spans="1:10" ht="13.5" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
+    <row r="69" spans="1:10" ht="13.5" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" ht="13.5" customHeight="1">
+    <row r="70" spans="1:10" ht="13.5" customHeight="1">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" ht="13.5" customHeight="1">
+    <row r="71" spans="1:10" ht="13.5" customHeight="1">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" ht="13.5" customHeight="1">
+    <row r="72" spans="1:10" ht="13.5" customHeight="1">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
+    <row r="73" spans="1:10" ht="13.5" customHeight="1">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" ht="13.5" customHeight="1">
+    <row r="74" spans="1:10" ht="13.5" customHeight="1">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" ht="13.5" customHeight="1">
+    <row r="75" spans="1:10" ht="13.5" customHeight="1">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" ht="13.5" customHeight="1">
+    <row r="76" spans="1:10" ht="13.5" customHeight="1">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" ht="13.5" customHeight="1">
+    <row r="77" spans="1:10" ht="13.5" customHeight="1">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" ht="13.5" customHeight="1">
+    <row r="78" spans="1:10" ht="13.5" customHeight="1">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" ht="13.5" customHeight="1">
+    <row r="79" spans="1:10" ht="13.5" customHeight="1">
       <c r="I79" s="1"/>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
+    <row r="80" spans="1:10" ht="13.5" customHeight="1">
       <c r="I80" s="1"/>
     </row>
-    <row r="81" ht="13.5" customHeight="1">
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" ht="13.5" customHeight="1">
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" ht="13.5" customHeight="1">
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
       <c r="A84" s="1"/>
     </row>
-    <row r="85" ht="13.5" customHeight="1">
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" ht="13.5" customHeight="1">
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" ht="13.5" customHeight="1">
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
     </row>
-    <row r="90" ht="13.5" customHeight="1">
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="A90" s="1"/>
     </row>
-    <row r="91" ht="13.5" customHeight="1">
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" ht="13.5" customHeight="1">
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" ht="13.5" customHeight="1">
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" ht="13.5" customHeight="1">
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
     </row>
-    <row r="96" ht="13.5" customHeight="1">
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
       <c r="A96" s="1"/>
     </row>
-    <row r="97" ht="13.5" customHeight="1">
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="I98" s="1"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="A100" s="1"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
       <c r="I104" s="1"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
       <c r="I107" s="1"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" ht="13.5" customHeight="1">
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
     </row>
-    <row r="115" ht="13.5" customHeight="1">
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="A115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" ht="13.5" customHeight="1">
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
     </row>
-    <row r="118" ht="13.5" customHeight="1">
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
       <c r="A118" s="1"/>
     </row>
-    <row r="119" ht="13.5" customHeight="1">
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
     </row>
-    <row r="123" ht="13.5" customHeight="1">
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" ht="13.5" customHeight="1">
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="I125" s="1"/>
     </row>
-    <row r="126" ht="13.5" customHeight="1">
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
     </row>
-    <row r="127" ht="13.5" customHeight="1">
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
     </row>
-    <row r="128" ht="13.5" customHeight="1">
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
       <c r="I128" s="1"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
       <c r="A129" s="1"/>
     </row>
-    <row r="130" ht="13.5" customHeight="1">
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
     </row>
-    <row r="131" ht="13.5" customHeight="1">
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" ht="13.5" customHeight="1">
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="A132" s="1"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
       <c r="I134" s="1"/>
     </row>
-    <row r="135" ht="13.5" customHeight="1">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
       <c r="I135" s="1"/>
     </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="136" spans="1:9" ht="13.5" customHeight="1">
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" spans="1:9" ht="13.5" customHeight="1">
       <c r="I137" s="1"/>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="138" spans="1:9" ht="13.5" customHeight="1">
       <c r="I138" s="1"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" spans="1:9" ht="13.5" customHeight="1">
       <c r="I139" s="1"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="141" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="142" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="143" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="145" ht="13.5" customHeight="1"/>
     <row r="146" ht="13.5" customHeight="1"/>
     <row r="147" ht="13.5" customHeight="1"/>
@@ -1974,9 +1994,8 @@
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFF8F4DB-9ACB-4D2A-8169-2D96C5079E01}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B86055-4729-40DF-827A-E8B87856D378}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Command</t>
   </si>
@@ -78,20 +78,313 @@
     <t>BgOff</t>
   </si>
   <si>
-    <t>Chapter1-3です</t>
-  </si>
-  <si>
     <t>Jump</t>
   </si>
   <si>
     <t>*chapter0104_Start</t>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：男の子の部屋</t>
+    <rPh sb="3" eb="4">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘヤ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希と約束を交わした夜から、
+僕の生活は何もかもが変わってしまった</t>
+    <rPh sb="3" eb="5">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セイカツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ひたすら書く毎日が始まった。
+書かずにはいられなかったからだ</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マイニチ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希にカッコつけたかったし、
+夢を叶えつつある有希への嫉妬もあった</t>
+    <rPh sb="15" eb="16">
+      <t>ユメ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シット</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕だって出来るんだぞって、
+頑張れるんだぞって、有希に見せたかった</t>
+    <rPh sb="0" eb="1">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>デキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガンバ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>小説投稿サイトや新人賞に投稿を続け、
+個人のSNSで宣伝を続けた</t>
+    <rPh sb="0" eb="2">
+      <t>ショウセツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>シンジンショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コジン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>センデン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ある時は僕の宣伝をウザがったリア友に、
+フォローを外されたり、文句を言われた</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センデン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ハズ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>モンク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ある時は小説投稿サイトのコメント欄で、
+酷評されて落ち込んだりもした</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウセツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コクヒョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>でも、立ち止まることができなかった。
+だって僕は、有希と……</t>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ボク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>大好きな人と、約束したのだから</t>
+    <rPh sb="0" eb="2">
+      <t>ダイス</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヤクソク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして有希が東京に行って半年ほど経って、
+春休みに入った頃……</t>
+    <rPh sb="6" eb="8">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハントシ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハルヤス</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コロ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>東京のライトノベル編集部から、
+旅費を持つから会いたいと連絡が来た</t>
+    <rPh sb="0" eb="2">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ヘンシュウブ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>リョヒ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>レンラク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちょうど春休みと重なったこともあって、
+僕は一人で上京することになった</t>
+    <rPh sb="4" eb="6">
+      <t>ハルヤス</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ボク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒトリ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM6</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>FadeOut</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">black
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +412,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -140,13 +441,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -163,6 +483,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -370,7 +694,7 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="7" width="5.109375" customWidth="1"/>
     <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="9" max="9" width="39.44140625" customWidth="1"/>
     <col min="10" max="10" width="8.21875" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="11.33203125" customWidth="1"/>
@@ -468,81 +792,123 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="I6" s="1"/>
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
+    <row r="8" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="27" customHeight="1">
+      <c r="I9" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="27.6" customHeight="1">
+      <c r="I10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.2" customHeight="1">
+      <c r="I12" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:12" ht="13.5" customHeight="1">
+    <row r="13" spans="1:12" ht="28.2" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="I13" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="13.5" customHeight="1">
+    <row r="14" spans="1:12" ht="28.2" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:12" ht="13.5" customHeight="1">
+    <row r="15" spans="1:12" ht="28.8" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:12" ht="13.5" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="I16" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="30" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I17" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="G18" s="9">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="33" customHeight="1">
+      <c r="A19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1"/>
@@ -1111,22 +1477,29 @@
     <row r="174" ht="13.5" customHeight="1"/>
     <row r="175" ht="13.5" customHeight="1"/>
     <row r="176" ht="13.5" customHeight="1"/>
-    <row r="177" ht="13.5" customHeight="1"/>
-    <row r="178" ht="13.5" customHeight="1"/>
-    <row r="179" ht="13.5" customHeight="1"/>
-    <row r="180" ht="13.5" customHeight="1"/>
-    <row r="181" ht="13.5" customHeight="1"/>
-    <row r="182" ht="13.5" customHeight="1"/>
-    <row r="183" ht="13.5" customHeight="1"/>
-    <row r="184" ht="13.5" customHeight="1"/>
-    <row r="185" ht="13.5" customHeight="1"/>
-    <row r="186" ht="13.5" customHeight="1"/>
-    <row r="187" ht="13.5" customHeight="1"/>
-    <row r="188" ht="13.5" customHeight="1"/>
-    <row r="189" ht="13.5" customHeight="1"/>
-    <row r="190" ht="13.5" customHeight="1"/>
-    <row r="191" ht="13.5" customHeight="1"/>
-    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="177" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="178" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="179" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A179" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="181" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="182" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="183" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="187" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="188" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="189" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="190" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="191" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="192" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="193" ht="13.5" customHeight="1"/>
     <row r="194" ht="13.5" customHeight="1"/>
     <row r="195" ht="13.5" customHeight="1"/>

--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3B86055-4729-40DF-827A-E8B87856D378}"/>
+  <xr:revisionPtr revIDLastSave="396" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DB22130-A4A4-41DD-9632-E6EF7587EF48}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0103" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="113">
   <si>
     <t>Command</t>
   </si>
@@ -377,6 +377,327 @@
   </si>
   <si>
     <t>FadeIn</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：都会の街並み</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>初めての東京。初めての編集者との面会。
+何より優先すべきことが、僕にはあった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希に会うことだ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>久しぶり、マネージャー！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>通常</t>
+  </si>
+  <si>
+    <t>浪川有希</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>おめでとう！　本当に頑張ったね！
+明日、編集さんと会うんでしょ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-1-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-1-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>まぁね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……有希と約束したから</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あははっ、自信満々だね。
+分かってたよ。あなたはやるって</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あなたのことは誰より分かるよ。
+子どもの頃からずっと一緒なんだもん</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-1合流</t>
+  </si>
+  <si>
+    <t>*選択肢0103-1合流</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そっか……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そうだね。約束したもんね。
+あの時、ちゃんと……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それじゃ、これでマネージャーは、
+マネージャーを引退だね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>約束通り、センセーって呼ぶよ。
+よろしくね、センセー♪</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ふぅ……私も頑張らなくちゃね。
+センセイの期待にも応えなくっちゃ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そういえば、有希の方はどうなのだろう？
+上京してから、あまり活動は知らない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>トーク番組にゲストで出演したり、
+SNSで公式アカウントを作ってはいるが……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>役者としての活動は見ていない</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-2-a</t>
+  </si>
+  <si>
+    <t>*選択肢0103-2-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希の方はどんな感じ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私？　ああ、私は……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>今は準備期間って感じかなぁ。
+こっちには色んな人たちがいて……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私を売り出すために、
+色々な人たちが頑張ってくれているの</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>こっちの学校に通いながらだけど、
+私も頑張って、色々と勉強中だよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>覚悟して飛び込んだつもりだったけど、
+それでも甘かったなぁって思うよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>勉強することや、
+知らないことは山ほどあって……ふぅ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>*選択肢0103-3-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-3-b</t>
+  </si>
+  <si>
+    <t>*選択肢0103-3-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>……疲れている？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>約束は大丈夫そう？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>え？
+ああ、大丈夫、大丈夫……！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ちゃんと頑張るよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-3合流</t>
+  </si>
+  <si>
+    <t>*選択肢0103-3合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>も、もちろんだよ！
+だってマネージャーは……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>いや、センセーは約束通り、
+ちゃんとセンセーになったんだし……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私も頑張るよ！　一生懸命！
+絶対に役者として成功してみせる！</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-3合流</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そ、それより、東京を案内するよ。
+今日は久しぶりに丸一日オフを貰えたから</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>秋葉原と中野、どっちも行けるよ。
+センセーのホテルはどこだっけ？</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-4-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>えっと……神保町だね</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>だったら古本屋さん巡りをしてもいいね。
+面白いお店がいっぱいあるよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>色んなジャンル専門の古本屋があったり、
+あとはカレーが名物だよ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>私、今はダイエット中なんだけど……
+今日はチートデイだから、付き合えるし</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>中野と秋葉原を巡ろう！</t>
+  </si>
+  <si>
+    <t>神保町をブラブラしよう</t>
+  </si>
+  <si>
+    <t>了解！
+ふふっ、今日は楽しみにしてたの</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-5-a</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-5-b</t>
+  </si>
+  <si>
+    <t>*選択肢0103-5-b</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-5合流</t>
+  </si>
+  <si>
+    <t>*選択肢0103-5合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*選択肢0103-5合流</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>明日も仕事だから、
+夜遅くまでは無理だけど……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>その日、僕と有希は
+短いけれど、とても楽しい一日をすごした</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>翌日、僕は編集部に行って、
+web小説の書籍化の話をした</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして編集さんから、
+加筆・修正する箇所の資料を貰った</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：ダイニングルーム</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>CharacterOff</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>浪川有希</t>
+  </si>
+  <si>
+    <t>なるべく長く一緒にいたい、かな。
+色んなことを話したいの</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM4</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -441,7 +762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -467,6 +788,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1058"/>
+  <dimension ref="A1:L1062"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -896,342 +1223,689 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="33" customHeight="1">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" ht="33" customHeight="1">
+      <c r="A21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G19">
+      <c r="G21" s="9">
         <v>1</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
+    <row r="22" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="I23" s="6" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="B24" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="A27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="I27" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
+      <c r="A28" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A30" s="1"/>
+      <c r="B30" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A32" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
+    <row r="33" spans="1:10" ht="14.4" customHeight="1">
+      <c r="B33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A35" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
+    <row r="37" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B38" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B39" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="I40" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I41" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="14.4" customHeight="1">
+      <c r="I42" s="6" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
+      <c r="A43" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="A44" t="s">
+        <v>64</v>
+      </c>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B45" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="27.6" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="B46" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A47" s="1"/>
+      <c r="B47" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A48" s="1"/>
+      <c r="B48" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
+    <row r="49" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B49" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B50" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="A51" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="I51" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
+      <c r="A52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="A53" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="27" customHeight="1">
+      <c r="B54" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="14.4" customHeight="1">
+      <c r="B55" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
+    <row r="58" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B58" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B59" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="A60" s="1"/>
+      <c r="B60" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
+      <c r="A61" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="I61" s="1"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" t="s">
+        <v>81</v>
+      </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1">
+    <row r="63" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B63" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B64" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A65" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="I65" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="7" t="s">
+        <v>90</v>
+      </c>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1">
+    <row r="67" spans="1:9" ht="30" customHeight="1">
+      <c r="A67" s="1"/>
+      <c r="B67" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="I67" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B68" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B69" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
+    <row r="73" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A73" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="C73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1">
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A74" s="5" t="s">
+        <v>99</v>
+      </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
+    <row r="75" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A75" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="I82" s="1"/>
+    <row r="76" spans="1:9" ht="15" customHeight="1">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="9"/>
+      <c r="I76" s="8"/>
+    </row>
+    <row r="77" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B77" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B78" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B79" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A80" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A81" s="13"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="1"/>
+      <c r="I81" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A82" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C82" s="1"/>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
+    <row r="83" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I83" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="26.4">
+      <c r="I84" s="6" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
       <c r="I85" s="1"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="1"/>
       <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
       <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="1"/>
       <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
       <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="I88" s="1"/>
+      <c r="A88" s="1"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
       <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="I89" s="1"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="I90" s="1"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="B91" s="1"/>
@@ -1244,83 +1918,80 @@
       <c r="I92" s="1"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A93" s="1"/>
       <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
+      <c r="A94" s="1"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
       <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="I95" s="1"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="I96" s="1"/>
     </row>
     <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
       <c r="I97" s="1"/>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
       <c r="I98" s="1"/>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
-      <c r="I99" s="1"/>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
       <c r="I101" s="1"/>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
       <c r="I102" s="1"/>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
       <c r="I103" s="1"/>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="1"/>
+      <c r="H104" s="1"/>
       <c r="I104" s="1"/>
     </row>
     <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
       <c r="I106" s="1"/>
     </row>
     <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
       <c r="I107" s="1"/>
     </row>
     <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
       <c r="I108" s="1"/>
     </row>
     <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
       <c r="I109" s="1"/>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
       <c r="I110" s="1"/>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
     <row r="112" spans="1:9" ht="13.5" customHeight="1">
@@ -1329,21 +2000,19 @@
       <c r="I112" s="1"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
       <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
       <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="B116" s="1"/>
@@ -1353,14 +2022,19 @@
     <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1">
       <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
+      <c r="A119" s="1"/>
       <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
@@ -1368,19 +2042,16 @@
       <c r="I120" s="1"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
       <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
@@ -1398,37 +2069,45 @@
     </row>
     <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
     </row>
     <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
     <row r="129" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="I129" s="1"/>
     </row>
     <row r="130" spans="1:9" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
     </row>
     <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
     </row>
     <row r="132" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
       <c r="I132" s="1"/>
     </row>
     <row r="133" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I133" s="1"/>
+      <c r="A133" s="1"/>
     </row>
     <row r="134" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
+      <c r="A134" s="1"/>
     </row>
     <row r="135" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
+      <c r="H135" s="1"/>
       <c r="I135" s="1"/>
     </row>
     <row r="136" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A136" s="1"/>
+      <c r="H136" s="1"/>
       <c r="I136" s="1"/>
     </row>
     <row r="137" spans="1:9" ht="13.5" customHeight="1">
@@ -1440,10 +2119,18 @@
     <row r="139" spans="1:9" ht="13.5" customHeight="1">
       <c r="I139" s="1"/>
     </row>
-    <row r="140" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="142" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="143" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I143" s="1"/>
+    </row>
     <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="145" ht="13.5" customHeight="1"/>
     <row r="146" ht="13.5" customHeight="1"/>
@@ -1479,18 +2166,18 @@
     <row r="176" ht="13.5" customHeight="1"/>
     <row r="177" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="178" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="179" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A179" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="179" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="180" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="181" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="182" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="183" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="183" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A183" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
@@ -2366,6 +3053,10 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DB22130-A4A4-41DD-9632-E6EF7587EF48}"/>
+  <xr:revisionPtr revIDLastSave="538" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89FD8016-B41C-4D19-8C80-C451B405F116}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0103" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="131">
   <si>
     <t>Command</t>
   </si>
@@ -697,15 +697,98 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>BGM4</t>
-    <phoneticPr fontId="3"/>
+    <t>BGM1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：黒</t>
+    <rPh sb="3" eb="4">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>それは凄い量で、ネットに載せたものを
+半分は書き直さないといけなかった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>福岡に帰った僕は、
+春休み丸々、原稿の修正に使った</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ようやく修正稿を提出したけど、
+また編集さんから直しの依頼が来た</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>書いては直すを繰り返すうち、
+僕は高校三年生になった</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>三年生になって初めての登校日、
+僕は朝ごはんを食べていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>その時、テレビから聞き慣れた声がした</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>有希の声だった。
+けど、テレビに映っていたのは……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>派手なメイクで、髪型も変わって、
+まるで別人になっていた</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>子どもの頃からずっと付けていた
+ヘアピンも外している</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>そして……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>本当に光栄です</t>
+  </si>
+  <si>
+    <t>今回は日本版主題歌を
+歌わせて頂くことになって……</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>一生懸命、歌いました。
+是非、劇場で楽しんでください</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僕は産まれて初めて、目と耳を疑った</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,13 +824,25 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -762,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -794,6 +889,23 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1014,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1062"/>
+  <dimension ref="A1:L1066"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1208,228 +1320,216 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:10" ht="30" customHeight="1">
+      <c r="A18" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="G18" s="9">
+      <c r="G18" s="18">
         <v>1</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="20" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:10" ht="28.8" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C20" s="9"/>
       <c r="G20" s="9"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:10" ht="33" customHeight="1">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A22" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G22" s="9">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" ht="33" customHeight="1">
+      <c r="I23" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="6" t="s">
+    <row r="24" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="I23" s="6" t="s">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="I25" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B24" s="7" t="s">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B26" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="7" t="s">
+    <row r="27" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I27" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A26" s="1" t="s">
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B29" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="I27" s="6" t="s">
+      <c r="C29" s="1"/>
+      <c r="I29" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A28" s="5" t="s">
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="7" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A31" s="1"/>
+      <c r="B31" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="7" t="s">
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I32" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A31" t="s">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A33" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A32" s="5" t="s">
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A34" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="14.4" customHeight="1">
-      <c r="B33" s="7" t="s">
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" ht="14.4" customHeight="1">
+      <c r="B35" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B34" s="7" t="s">
+    <row r="36" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B36" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I36" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A35" s="5" t="s">
+    <row r="37" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A37" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>53</v>
       </c>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A36" s="5" t="s">
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A38" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B37" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B38" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" ht="28.8" customHeight="1">
       <c r="B39" s="7" t="s">
         <v>44</v>
       </c>
@@ -1437,68 +1537,66 @@
         <v>43</v>
       </c>
       <c r="I39" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B40" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="I40" s="6" t="s">
+    <row r="42" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="I42" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="28.8" customHeight="1">
-      <c r="I41" s="6" t="s">
+    <row r="43" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I43" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.4" customHeight="1">
-      <c r="I42" s="6" t="s">
+    <row r="44" spans="1:9" ht="14.4" customHeight="1">
+      <c r="I44" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A43" s="5" t="s">
+    <row r="45" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A45" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I45" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A44" t="s">
+    <row r="46" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A46" t="s">
         <v>64</v>
       </c>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B45" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A47" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" ht="13.5" customHeight="1">
       <c r="B47" s="7" t="s">
         <v>44</v>
       </c>
@@ -1506,10 +1604,10 @@
         <v>43</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="28.8" customHeight="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="27.6" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="7" t="s">
         <v>44</v>
@@ -1518,11 +1616,11 @@
         <v>43</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" ht="28.2" customHeight="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A49" s="1"/>
       <c r="B49" s="7" t="s">
         <v>44</v>
       </c>
@@ -1530,10 +1628,11 @@
         <v>43</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A50" s="1"/>
       <c r="B50" s="7" t="s">
         <v>44</v>
       </c>
@@ -1541,250 +1640,255 @@
         <v>43</v>
       </c>
       <c r="I50" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B51" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B52" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A51" s="5" t="s">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A53" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="I51" s="6" t="s">
+      <c r="C53" s="1"/>
+      <c r="I53" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A52" s="1" t="s">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A54" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I54" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A53" s="1" t="s">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="27" customHeight="1">
-      <c r="B54" s="7" t="s">
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="27" customHeight="1">
+      <c r="B56" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C56" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I56" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="14.4" customHeight="1">
-      <c r="B55" s="7" t="s">
+    <row r="57" spans="1:10" ht="14.4" customHeight="1">
+      <c r="B57" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C57" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="I57" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A56" s="1" t="s">
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A57" s="1" t="s">
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A59" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B58" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B59" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1">
-      <c r="A60" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" ht="28.2" customHeight="1">
       <c r="B60" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B61" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" customHeight="1">
+      <c r="A62" s="1"/>
+      <c r="B62" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="I62" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A61" s="1" t="s">
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A62" t="s">
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A64" t="s">
         <v>81</v>
       </c>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B63" s="7" t="s">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B65" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C65" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="I65" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B64" s="7" t="s">
+    <row r="66" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B66" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C66" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="I66" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A65" s="5" t="s">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B67" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="1"/>
-      <c r="I65" s="6" t="s">
+      <c r="C67" s="1"/>
+      <c r="I67" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A66" s="7" t="s">
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" ht="30" customHeight="1">
-      <c r="A67" s="1"/>
-      <c r="B67" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B68" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" ht="30" customHeight="1">
+      <c r="A69" s="1"/>
       <c r="B69" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="H69" s="1"/>
       <c r="I69" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B70" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B71" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I71" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A70" s="1" t="s">
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I72" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="1" t="s">
+    <row r="73" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A73" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1" t="s">
+      <c r="H73" s="1"/>
+      <c r="I73" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A72" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A73" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
     </row>
     <row r="74" spans="1:9" ht="13.5" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -1794,43 +1898,39 @@
       <c r="A75" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>103</v>
+      <c r="B75" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="1:9" ht="15" customHeight="1">
-      <c r="A76" t="s">
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A76" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A77" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" ht="15" customHeight="1">
+      <c r="A78" t="s">
         <v>101</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="9"/>
-      <c r="I76" s="8"/>
-    </row>
-    <row r="77" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B78" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B78" s="7"/>
+      <c r="C78" s="9"/>
+      <c r="I78" s="8"/>
+    </row>
+    <row r="79" spans="1:9" ht="28.2" customHeight="1">
       <c r="B79" s="7" t="s">
         <v>44</v>
       </c>
@@ -1838,180 +1938,245 @@
         <v>43</v>
       </c>
       <c r="I79" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B80" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B81" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A80" s="13" t="s">
+    <row r="82" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A82" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B82" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C80" s="9"/>
-      <c r="I80" s="6"/>
-    </row>
-    <row r="81" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A81" s="13"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="1"/>
-      <c r="I81" s="6" t="s">
+      <c r="C82" s="9"/>
+      <c r="I82" s="6"/>
+    </row>
+    <row r="83" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A83" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="I83" s="6"/>
+    </row>
+    <row r="84" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A84" s="13"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="1"/>
+      <c r="I84" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A82" s="13" t="s">
+    <row r="85" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A85" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B85" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" ht="28.8" customHeight="1">
-      <c r="I83" s="6" t="s">
+      <c r="C85" s="1"/>
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I86" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="26.4">
-      <c r="I84" s="6" t="s">
+    <row r="87" spans="1:10" ht="26.4">
+      <c r="I87" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+    <row r="88" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I88" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="27" customHeight="1">
+      <c r="A89" s="1"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I89" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A90" s="1"/>
       <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I90" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A91" s="1"/>
+      <c r="I91" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="28.2" customHeight="1">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A93" s="1"/>
+      <c r="I92" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A93" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="I93" s="6"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B94" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="I94" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="30.6" customHeight="1">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
-      <c r="I95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I95" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="28.8" customHeight="1">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
-      <c r="I96" s="1"/>
-    </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I96" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A97" s="1"/>
       <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="I97" s="1"/>
+      <c r="I97" s="14" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="I98" s="1"/>
+      <c r="A98" s="1"/>
+      <c r="I98" s="14" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-    </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-    </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I102" s="1"/>
+      <c r="B99" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="30" customHeight="1">
+      <c r="B100" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B101" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="13.8" customHeight="1">
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="I102" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-      <c r="I103" s="1"/>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
     </row>
     <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
     <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
       <c r="I106" s="1"/>
     </row>
     <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
       <c r="I107" s="1"/>
     </row>
     <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1"/>
+      <c r="H108" s="1"/>
       <c r="I108" s="1"/>
     </row>
     <row r="109" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
       <c r="I109" s="1"/>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
       <c r="I110" s="1"/>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
     <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
       <c r="I112" s="1"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
       <c r="I114" s="1"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
       <c r="I115" s="1"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1">
@@ -2020,21 +2185,19 @@
       <c r="I116" s="1"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
       <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
       <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
       <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
       <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
@@ -2044,14 +2207,19 @@
     <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
+      <c r="A123" s="1"/>
       <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
@@ -2059,95 +2227,108 @@
       <c r="I124" s="1"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="I125" s="1"/>
     </row>
     <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
     </row>
     <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
       <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
       <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
     </row>
     <row r="128" spans="1:10" ht="13.5" customHeight="1">
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" spans="1:9" ht="13.5" customHeight="1">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="I129" s="1"/>
     </row>
-    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
     </row>
-    <row r="131" spans="1:9" ht="13.5" customHeight="1">
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
-    </row>
-    <row r="132" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A133" s="1"/>
-    </row>
-    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
       <c r="A134" s="1"/>
-    </row>
-    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
       <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A136" s="1"/>
-      <c r="H136" s="1"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
       <c r="I136" s="1"/>
     </row>
-    <row r="137" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" spans="1:9" ht="13.5" customHeight="1">
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="H139" s="1"/>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" spans="1:9" ht="13.5" customHeight="1">
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="1"/>
+      <c r="H140" s="1"/>
       <c r="I140" s="1"/>
     </row>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
       <c r="I141" s="1"/>
     </row>
-    <row r="142" spans="1:9" ht="13.5" customHeight="1">
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
       <c r="I142" s="1"/>
     </row>
-    <row r="143" spans="1:9" ht="13.5" customHeight="1">
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
       <c r="I143" s="1"/>
     </row>
-    <row r="144" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="149" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -2170,18 +2351,18 @@
     <row r="180" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="181" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="182" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="183" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A183" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="183" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="187" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="187" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A187" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="188" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="189" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="190" spans="1:2" ht="13.5" customHeight="1"/>
@@ -3057,6 +3238,10 @@
     <row r="1060" ht="13.5" customHeight="1"/>
     <row r="1061" ht="13.5" customHeight="1"/>
     <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="538" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89FD8016-B41C-4D19-8C80-C451B405F116}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0103" sheetId="1" r:id="rId1"/>

--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="538" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89FD8016-B41C-4D19-8C80-C451B405F116}"/>
+  <xr:revisionPtr revIDLastSave="540" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABB3E5D-8665-4078-86AA-3E56C317F0A9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6600" yWindow="2820" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0103" sheetId="1" r:id="rId1"/>
@@ -1478,8 +1478,8 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A33" t="s">
-        <v>17</v>
+      <c r="A33" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>54</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="73" spans="1:9" ht="13.5" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>100</v>

--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="540" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABB3E5D-8665-4078-86AA-3E56C317F0A9}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6600" yWindow="2820" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0103" sheetId="1" r:id="rId1"/>

--- a/Assets/test260903/chapter0103.xlsx
+++ b/Assets/test260903/chapter0103.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="540" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABB3E5D-8665-4078-86AA-3E56C317F0A9}"/>
+  <xr:revisionPtr revIDLastSave="560" documentId="11_F3C2E2C338C096042E83A027A8BF203497348038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9214B74C-FF83-4ECD-A0FD-8926EFAF4743}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0103" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="133">
   <si>
     <t>Command</t>
   </si>
@@ -371,11 +371,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">black
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>FadeIn</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -593,10 +588,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>通常</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>秋葉原と中野、どっちも行けるよ。
 センセーのホテルはどこだっけ？</t>
     <phoneticPr fontId="3"/>
@@ -782,6 +773,18 @@
   </si>
   <si>
     <t>&lt;Off&gt;</t>
+  </si>
+  <si>
+    <t>喜び</t>
+  </si>
+  <si>
+    <t>悲しみ</t>
+  </si>
+  <si>
+    <t>怒り</t>
+  </si>
+  <si>
+    <t>照れ</t>
   </si>
 </sst>
 </file>
@@ -857,7 +860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -880,9 +883,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1321,24 +1321,24 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <v>1</v>
       </c>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:10" ht="28.8" customHeight="1">
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="20" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="9"/>
       <c r="G20" s="9"/>
@@ -1357,8 +1357,8 @@
       <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>112</v>
+      <c r="B21" s="16" t="s">
+        <v>110</v>
       </c>
       <c r="C21" s="9"/>
       <c r="G21" s="9"/>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="22" spans="1:10" ht="28.8" customHeight="1">
       <c r="A22" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="11" t="s">
         <v>37</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="G22" s="9">
         <v>1</v>
@@ -1385,67 +1385,67 @@
       <c r="A24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="I25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1">
       <c r="B26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C26" s="5" t="s">
+        <v>129</v>
+      </c>
       <c r="I26" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="27.6" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="A28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="I28" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="1"/>
       <c r="I29" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1454,334 +1454,334 @@
     <row r="31" spans="1:10" ht="28.2" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C31" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="I31" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10" ht="28.2" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:9" ht="14.4" customHeight="1">
       <c r="B35" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="28.8" customHeight="1">
       <c r="B36" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" ht="13.5" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9" ht="28.8" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="27.6" customHeight="1">
       <c r="B40" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C40" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="I40" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="28.8" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="28.8" customHeight="1">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="I42" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="28.8" customHeight="1">
       <c r="I43" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="14.4" customHeight="1">
       <c r="I44" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="13.5" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="13.5" customHeight="1">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9" ht="13.5" customHeight="1">
       <c r="B47" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C47" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="I47" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="27.6" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="28.8" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="28.8" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" ht="28.2" customHeight="1">
       <c r="B51" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C51" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="I51" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="28.8" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C52" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="I52" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" s="1"/>
       <c r="I53" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10" ht="27" customHeight="1">
       <c r="B56" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="14.4" customHeight="1">
       <c r="B57" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C57" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>80</v>
+      <c r="C57" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:10" ht="28.2" customHeight="1">
       <c r="B60" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="28.2" customHeight="1">
       <c r="B61" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="30" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>88</v>
+        <v>43</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I63" s="1"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1789,41 +1789,41 @@
     </row>
     <row r="65" spans="1:9" ht="28.2" customHeight="1">
       <c r="B65" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="28.8" customHeight="1">
       <c r="B66" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="13.5" customHeight="1">
       <c r="A67" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C67" s="1"/>
       <c r="I67" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="13.5" customHeight="1">
       <c r="A68" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B68" s="1"/>
       <c r="I68" s="1"/>
@@ -1831,64 +1831,64 @@
     <row r="69" spans="1:9" ht="30" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C69" s="9" t="s">
         <v>43</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="28.2" customHeight="1">
       <c r="B70" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28.2" customHeight="1">
       <c r="B71" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="13.5" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="13.5" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="13.5" customHeight="1">
       <c r="A74" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -1896,17 +1896,17 @@
     </row>
     <row r="75" spans="1:9" ht="13.5" customHeight="1">
       <c r="A75" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" spans="1:9" ht="13.5" customHeight="1">
       <c r="A76" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -1914,17 +1914,17 @@
     </row>
     <row r="77" spans="1:9" ht="13.5" customHeight="1">
       <c r="A77" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C77" s="1"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" spans="1:9" ht="15" customHeight="1">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="9"/>
@@ -1932,95 +1932,95 @@
     </row>
     <row r="79" spans="1:9" ht="28.2" customHeight="1">
       <c r="B79" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C79" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C79" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="I79" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="27.6" customHeight="1">
       <c r="B80" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="27.6" customHeight="1">
       <c r="B81" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C81" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="C81" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="I81" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A82" s="13" t="s">
-        <v>109</v>
+      <c r="A82" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C82" s="9"/>
       <c r="I82" s="6"/>
     </row>
     <row r="83" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C83" s="9"/>
       <c r="I83" s="6"/>
     </row>
     <row r="84" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A84" s="13"/>
+      <c r="A84" s="12"/>
       <c r="B84" s="7"/>
       <c r="C84" s="1"/>
       <c r="I84" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C85" s="1"/>
       <c r="J85" s="1"/>
     </row>
     <row r="86" spans="1:10" ht="28.8" customHeight="1">
       <c r="I86" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="26.4">
       <c r="I87" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="28.8" customHeight="1">
       <c r="I88" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="27" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="I89" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J89" s="1"/>
     </row>
@@ -2028,26 +2028,26 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="I90" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J90" s="1"/>
     </row>
     <row r="91" spans="1:10" ht="28.2" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="I91" s="14" t="s">
-        <v>117</v>
+      <c r="I91" s="13" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="28.2" customHeight="1">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="I92" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A93" s="15" t="s">
-        <v>129</v>
+      <c r="A93" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2055,78 +2055,78 @@
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C94" s="1"/>
       <c r="I94" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="30.6" customHeight="1">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="I95" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="28.8" customHeight="1">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="I96" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="28.8" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
-      <c r="I97" s="14" t="s">
-        <v>122</v>
+      <c r="I97" s="13" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="13.5" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="I98" s="14" t="s">
-        <v>123</v>
+      <c r="I98" s="13" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="B99" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>130</v>
+        <v>43</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="30" customHeight="1">
       <c r="B100" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C100" s="16" t="s">
-        <v>130</v>
+        <v>43</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="28.2" customHeight="1">
       <c r="B101" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C101" s="16" t="s">
-        <v>130</v>
+        <v>43</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="13.8" customHeight="1">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
-      <c r="I102" s="12" t="s">
-        <v>127</v>
+      <c r="I102" s="11" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
